--- a/output/laminas_comunales/comunal_s_fonasa_a_2023_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2023_valparaiso.xlsx
@@ -375,436 +375,436 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Viña del Mar</t>
+          <t>Petorca</t>
         </is>
       </c>
       <c r="C2">
-        <v>268310</v>
+        <v>94.83359133126935</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Juan Fernández</t>
         </is>
       </c>
       <c r="C3">
-        <v>265228</v>
+        <v>94.36133486766398</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quilpué</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="C4">
-        <v>139713</v>
+        <v>93.44978165938865</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Villa Alemana</t>
+          <t>Santa María</t>
         </is>
       </c>
       <c r="C5">
-        <v>113336</v>
+        <v>92.95162278015921</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Catemu</t>
         </is>
       </c>
       <c r="C6">
-        <v>93411</v>
+        <v>92.90699149854079</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quillota</t>
+          <t>Isla de Pascua</t>
         </is>
       </c>
       <c r="C7">
-        <v>87677</v>
+        <v>92.69315930544225</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>San Felipe</t>
+          <t>Putaendo</t>
         </is>
       </c>
       <c r="C8">
-        <v>73366</v>
+        <v>92.63622974963181</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Cabildo</t>
         </is>
       </c>
       <c r="C9">
-        <v>58466</v>
+        <v>91.23634120549876</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Limache</t>
+          <t>La Ligua</t>
         </is>
       </c>
       <c r="C10">
-        <v>49364</v>
+        <v>91.15898072743772</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>La Ligua</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="C11">
-        <v>38171</v>
+        <v>90.98798983080565</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>5503</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Concón</t>
+          <t>Hijuelas</t>
         </is>
       </c>
       <c r="C12">
-        <v>35131</v>
+        <v>90.98334904178448</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Quintero</t>
+          <t>Panquehue</t>
         </is>
       </c>
       <c r="C13">
-        <v>32303</v>
+        <v>90.59163059163059</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>El Tabo</t>
         </is>
       </c>
       <c r="C14">
-        <v>28614</v>
+        <v>88.89851723473907</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>El Quisco</t>
         </is>
       </c>
       <c r="C15">
-        <v>25680</v>
+        <v>88.4277697320782</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Puchuncaví</t>
+          <t>Nogales</t>
         </is>
       </c>
       <c r="C16">
-        <v>21985</v>
+        <v>88.23310754997522</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nogales</t>
+          <t>San Felipe</t>
         </is>
       </c>
       <c r="C17">
-        <v>21363</v>
+        <v>88.11991784474579</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5504</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>La Cruz</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="C18">
-        <v>20881</v>
+        <v>87.75416321648726</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cabildo</t>
+          <t>Calle Larga</t>
         </is>
       </c>
       <c r="C19">
-        <v>20707</v>
+        <v>86.85828016156412</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5503</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hijuelas</t>
+          <t>Quintero</t>
         </is>
       </c>
       <c r="C20">
-        <v>20272</v>
+        <v>86.81035177770015</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>El Quisco</t>
+          <t>Puchuncaví</t>
         </is>
       </c>
       <c r="C21">
-        <v>19539</v>
+        <v>86.76006314127861</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>El Tabo</t>
+          <t>Limache</t>
         </is>
       </c>
       <c r="C22">
-        <v>18466</v>
+        <v>86.73589513819338</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Olmué</t>
+          <t>Quillota</t>
         </is>
       </c>
       <c r="C23">
-        <v>18390</v>
+        <v>86.52705543329155</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>San Esteban</t>
+          <t>Olmué</t>
         </is>
       </c>
       <c r="C24">
-        <v>18091</v>
+        <v>86.1398660358799</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Putaendo</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="C25">
-        <v>17612</v>
+        <v>85.92829697209245</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Algarrobo</t>
+          <t>San Esteban</t>
         </is>
       </c>
       <c r="C26">
-        <v>16775</v>
+        <v>85.42355274341297</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Santa María</t>
+          <t>Papudo</t>
         </is>
       </c>
       <c r="C27">
-        <v>15179</v>
+        <v>84.92073245667936</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Calle Larga</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="C28">
-        <v>14838</v>
+        <v>83.33951022037232</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Catemu</t>
+          <t>Villa Alemana</t>
         </is>
       </c>
       <c r="C29">
-        <v>14644</v>
+        <v>83.02821183417214</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Santo Domingo</t>
+          <t>Quilpué</t>
         </is>
       </c>
       <c r="C30">
-        <v>11977</v>
+        <v>81.91860499205517</v>
       </c>
     </row>
     <row r="31">
@@ -819,97 +819,97 @@
         </is>
       </c>
       <c r="C31">
-        <v>10401</v>
+        <v>81.58926890492626</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Petorca</t>
+          <t>Algarrobo</t>
         </is>
       </c>
       <c r="C32">
-        <v>9802</v>
+        <v>79.6874257754976</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>5405</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Panquehue</t>
+          <t>Zapallar</t>
         </is>
       </c>
       <c r="C33">
-        <v>9417</v>
+        <v>78.38477647273058</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Zapallar</t>
+          <t>La Cruz</t>
         </is>
       </c>
       <c r="C34">
-        <v>8609</v>
+        <v>78.12406465130201</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5201</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Isla de Pascua</t>
+          <t>Viña del Mar</t>
         </is>
       </c>
       <c r="C35">
-        <v>7954</v>
+        <v>77.39324572232927</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Papudo</t>
+          <t>Santo Domingo</t>
         </is>
       </c>
       <c r="C36">
-        <v>6910</v>
+        <v>75.07678806494076</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Juan Fernández</t>
+          <t>Concón</t>
         </is>
       </c>
       <c r="C37">
-        <v>820</v>
+        <v>64.36017220848218</v>
       </c>
     </row>
   </sheetData>
@@ -965,7 +965,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
